--- a/assets/infobasica/planilhas/aula17_nivel2.xlsx
+++ b/assets/infobasica/planilhas/aula17_nivel2.xlsx
@@ -6494,7 +6494,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
